--- a/MR_UKBiobank/BinaryData/PhenotypingR.xlsx
+++ b/MR_UKBiobank/BinaryData/PhenotypingR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UK_Biobank_dataset\vers7\Sclerostin_vs_CVD_MR\MR_UKBiobank\BinaryData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\martaa\Documents\GitHub\MR_Sclerostin\MR_UKBiobank\BinaryData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA586D58-39DB-48AC-A6D4-F9DA3AFC958F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D084368-343B-4F3D-8ED8-BC2D991A0DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11596" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="12735" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CAD" sheetId="1" r:id="rId1"/>
@@ -1760,7 +1760,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1906,6 +1906,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2205,7 +2212,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -2248,6 +2255,8 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2274,7 +2283,7 @@
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -2312,6 +2321,8 @@
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="43" xr:uid="{FA61A203-7ACC-45F2-B7BF-3F8000327AA4}"/>
+    <cellStyle name="Normal 3" xfId="42" xr:uid="{E9132A1B-4215-4D38-B075-055B52078D5B}"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
@@ -2629,9 +2640,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2645,7 +2656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>4</v>
       </c>
@@ -2653,32 +2664,33 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{261412A6-2DE0-4574-B276-596F76AFBF98}">
   <dimension ref="A1:E238"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>271</v>
       </c>
@@ -2695,7 +2707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>3005</v>
       </c>
@@ -2712,7 +2724,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1">
         <v>20002</v>
@@ -2727,7 +2739,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>20002</v>
@@ -2742,7 +2754,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>20002</v>
@@ -2757,7 +2769,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>20002</v>
@@ -2772,7 +2784,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>20002</v>
@@ -2787,7 +2799,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>20002</v>
@@ -2802,7 +2814,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>20002</v>
@@ -2817,7 +2829,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>20002</v>
@@ -2832,7 +2844,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -2843,7 +2855,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -2854,7 +2866,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -2865,7 +2877,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -2876,7 +2888,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -2887,7 +2899,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -2898,7 +2910,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -2909,7 +2921,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -2920,7 +2932,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -2931,7 +2943,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -2942,7 +2954,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -2953,7 +2965,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -2964,7 +2976,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -2975,7 +2987,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -2986,7 +2998,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2997,7 +3009,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -3008,7 +3020,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -3019,7 +3031,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -3030,7 +3042,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -3039,7 +3051,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -3048,7 +3060,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -3057,7 +3069,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -3066,7 +3078,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -3075,7 +3087,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -3084,7 +3096,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -3093,7 +3105,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -3102,7 +3114,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -3111,7 +3123,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -3120,7 +3132,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -3129,7 +3141,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -3138,7 +3150,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -3147,7 +3159,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -3156,7 +3168,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -3165,7 +3177,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -3174,7 +3186,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -3183,7 +3195,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -3192,7 +3204,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -3201,7 +3213,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -3210,7 +3222,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -3219,7 +3231,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -3228,7 +3240,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -3237,7 +3249,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -3246,7 +3258,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -3255,7 +3267,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -3264,7 +3276,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -3273,7 +3285,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -3282,7 +3294,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -3291,7 +3303,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -3300,7 +3312,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -3309,7 +3321,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -3318,7 +3330,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -3327,7 +3339,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -3336,7 +3348,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -3345,7 +3357,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -3354,7 +3366,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -3363,7 +3375,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -3372,7 +3384,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -3381,7 +3393,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -3390,7 +3402,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -3399,7 +3411,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -3408,7 +3420,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3417,7 +3429,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3426,7 +3438,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3435,7 +3447,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3444,7 +3456,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3453,7 +3465,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3462,7 +3474,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3471,7 +3483,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3480,7 +3492,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3489,7 +3501,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3498,7 +3510,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3507,7 +3519,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3516,7 +3528,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3525,7 +3537,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3534,7 +3546,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3543,7 +3555,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3552,7 +3564,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3561,7 +3573,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3570,7 +3582,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3579,7 +3591,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3588,7 +3600,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3597,7 +3609,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3606,7 +3618,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3615,7 +3627,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3624,7 +3636,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3633,7 +3645,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3642,7 +3654,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3651,7 +3663,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3660,7 +3672,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3669,7 +3681,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3678,7 +3690,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3687,7 +3699,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3696,7 +3708,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3705,7 +3717,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -3714,7 +3726,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -3723,7 +3735,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -3732,7 +3744,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -3741,7 +3753,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -3750,7 +3762,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -3759,7 +3771,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -3768,7 +3780,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -3777,7 +3789,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -3786,7 +3798,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -3795,7 +3807,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -3804,7 +3816,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -3813,7 +3825,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -3822,7 +3834,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -3831,7 +3843,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -3840,7 +3852,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -3849,7 +3861,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -3858,7 +3870,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -3867,7 +3879,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -3876,7 +3888,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -3885,7 +3897,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -3894,7 +3906,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -3903,7 +3915,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -3912,7 +3924,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -3921,7 +3933,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -3930,7 +3942,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -3939,7 +3951,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -3948,7 +3960,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -3957,7 +3969,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -3966,7 +3978,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -3975,7 +3987,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -3984,7 +3996,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -3993,7 +4005,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -4002,7 +4014,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -4011,7 +4023,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -4020,7 +4032,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -4029,7 +4041,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -4038,7 +4050,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -4047,7 +4059,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -4056,7 +4068,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -4065,7 +4077,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -4074,7 +4086,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -4083,7 +4095,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -4092,7 +4104,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -4101,7 +4113,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -4110,7 +4122,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -4119,7 +4131,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -4128,7 +4140,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -4137,7 +4149,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -4146,7 +4158,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -4155,7 +4167,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -4164,7 +4176,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -4173,7 +4185,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -4182,7 +4194,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -4191,7 +4203,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -4200,7 +4212,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -4209,7 +4221,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -4218,7 +4230,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -4227,7 +4239,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -4236,7 +4248,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -4245,7 +4257,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -4254,7 +4266,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -4263,7 +4275,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -4272,7 +4284,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -4281,7 +4293,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -4290,7 +4302,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -4299,7 +4311,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -4308,7 +4320,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -4317,7 +4329,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -4326,7 +4338,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -4335,7 +4347,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -4344,7 +4356,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -4353,7 +4365,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -4362,7 +4374,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -4371,7 +4383,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -4380,7 +4392,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -4389,7 +4401,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -4398,7 +4410,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -4407,7 +4419,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -4416,7 +4428,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -4425,7 +4437,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -4434,7 +4446,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -4443,7 +4455,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -4452,7 +4464,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -4461,7 +4473,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -4470,7 +4482,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -4479,7 +4491,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -4488,7 +4500,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -4497,7 +4509,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -4506,7 +4518,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -4515,7 +4527,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -4524,7 +4536,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -4533,7 +4545,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -4542,7 +4554,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -4551,7 +4563,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -4560,7 +4572,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -4569,7 +4581,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -4578,7 +4590,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -4587,7 +4599,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -4596,7 +4608,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -4605,7 +4617,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -4614,7 +4626,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -4623,7 +4635,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -4632,7 +4644,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -4641,7 +4653,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -4650,7 +4662,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -4659,7 +4671,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -4668,7 +4680,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -4677,7 +4689,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -4686,7 +4698,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -4695,7 +4707,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -4704,7 +4716,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -4713,7 +4725,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -4722,7 +4734,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -4731,7 +4743,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -4740,7 +4752,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -4749,7 +4761,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -4758,7 +4770,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -4767,7 +4779,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -4776,7 +4788,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -4785,7 +4797,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -4794,7 +4806,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -4803,7 +4815,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -4812,7 +4824,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -4821,7 +4833,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -4830,7 +4842,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -4839,7 +4851,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -4848,7 +4860,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -4857,7 +4869,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -4866,7 +4878,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -4875,7 +4887,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -4884,7 +4896,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -4893,7 +4905,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -4902,7 +4914,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -4911,7 +4923,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -4926,9 +4938,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{856DDF52-BBDB-4EA2-B941-8BC241E82723}">
   <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4942,7 +4954,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>20002</v>
       </c>
@@ -4957,7 +4969,7 @@
       </c>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
@@ -4968,7 +4980,7 @@
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
@@ -4979,7 +4991,7 @@
       </c>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
@@ -4990,7 +5002,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
@@ -5001,7 +5013,7 @@
       </c>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
@@ -5012,7 +5024,7 @@
       </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
@@ -5023,7 +5035,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
@@ -5034,7 +5046,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
@@ -5045,7 +5057,7 @@
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
@@ -5056,7 +5068,7 @@
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
@@ -5067,7 +5079,7 @@
       </c>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
@@ -5078,7 +5090,7 @@
       </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
@@ -5089,7 +5101,7 @@
       </c>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
@@ -5100,7 +5112,7 @@
       </c>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
@@ -5111,7 +5123,7 @@
       </c>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
@@ -5122,7 +5134,7 @@
       </c>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1" t="s">
@@ -5133,7 +5145,7 @@
       </c>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
@@ -5144,7 +5156,7 @@
       </c>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -5153,7 +5165,7 @@
       </c>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -5162,7 +5174,7 @@
       </c>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -5171,7 +5183,7 @@
       </c>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -5180,7 +5192,7 @@
       </c>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -5189,7 +5201,7 @@
       </c>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -5198,7 +5210,7 @@
       </c>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -5207,7 +5219,7 @@
       </c>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -5216,7 +5228,7 @@
       </c>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -5225,7 +5237,7 @@
       </c>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -5234,7 +5246,7 @@
       </c>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -5243,7 +5255,7 @@
       </c>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -5252,7 +5264,7 @@
       </c>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -5261,7 +5273,7 @@
       </c>
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -5270,7 +5282,7 @@
       </c>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -5279,7 +5291,7 @@
       </c>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -5288,7 +5300,7 @@
       </c>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -5297,7 +5309,7 @@
       </c>
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -5306,7 +5318,7 @@
       </c>
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -5315,7 +5327,7 @@
       </c>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -5324,7 +5336,7 @@
       </c>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -5333,7 +5345,7 @@
       </c>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -5342,7 +5354,7 @@
       </c>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -5351,7 +5363,7 @@
       </c>
       <c r="E42" s="1"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -5368,9 +5380,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FC0A611-5C9E-471A-A120-BDF2E60ADC52}">
   <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5384,7 +5396,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>20002</v>
       </c>
@@ -5399,7 +5411,7 @@
       </c>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
@@ -5410,7 +5422,7 @@
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="2" t="s">
@@ -5421,7 +5433,7 @@
       </c>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="2" t="s">
@@ -5432,7 +5444,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="2" t="s">
@@ -5443,7 +5455,7 @@
       </c>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
@@ -5454,7 +5466,7 @@
       </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="2" t="s">
@@ -5465,7 +5477,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="2" t="s">
@@ -5476,7 +5488,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="2" t="s">
@@ -5487,7 +5499,7 @@
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="2" t="s">
@@ -5498,7 +5510,7 @@
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -5507,7 +5519,7 @@
       </c>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -5516,7 +5528,7 @@
       </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -5525,7 +5537,7 @@
       </c>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -5534,7 +5546,7 @@
       </c>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -5543,28 +5555,28 @@
       </c>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -5579,9 +5591,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA5AD643-E3CB-4B9F-BDE3-9FE6AE56EFA1}">
   <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>271</v>
       </c>
@@ -5598,7 +5613,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>3894</v>
       </c>
@@ -5616,7 +5631,7 @@
       </c>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -5628,7 +5643,7 @@
       </c>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -5640,7 +5655,7 @@
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -5652,7 +5667,7 @@
       </c>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -5664,7 +5679,7 @@
       </c>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -5676,7 +5691,7 @@
       </c>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -5688,7 +5703,7 @@
       </c>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -5700,7 +5715,7 @@
       </c>
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -5712,7 +5727,7 @@
       </c>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -5724,7 +5739,7 @@
       </c>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -5736,7 +5751,7 @@
       </c>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -5748,7 +5763,7 @@
       </c>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -5760,7 +5775,7 @@
       </c>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -5772,7 +5787,7 @@
       </c>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -5784,7 +5799,7 @@
       </c>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -5796,7 +5811,7 @@
       </c>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -5808,7 +5823,7 @@
       </c>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -5820,7 +5835,7 @@
       </c>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -5832,7 +5847,7 @@
       </c>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -5844,7 +5859,7 @@
       </c>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -5856,7 +5871,7 @@
       </c>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -5866,7 +5881,7 @@
       </c>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -5876,7 +5891,7 @@
       </c>
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -5886,7 +5901,7 @@
       </c>
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -5896,7 +5911,7 @@
       </c>
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -5906,7 +5921,7 @@
       </c>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -5916,7 +5931,7 @@
       </c>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -5926,7 +5941,7 @@
       </c>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -5936,7 +5951,7 @@
       </c>
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -5946,7 +5961,7 @@
       </c>
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -5956,7 +5971,7 @@
       </c>
       <c r="F32" s="1"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -5966,7 +5981,7 @@
       </c>
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -5976,7 +5991,7 @@
       </c>
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -5986,7 +6001,7 @@
       </c>
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -5996,7 +6011,7 @@
       </c>
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -6006,7 +6021,7 @@
       </c>
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -6016,7 +6031,7 @@
       </c>
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -6026,7 +6041,7 @@
       </c>
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -6036,7 +6051,7 @@
       </c>
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -6046,7 +6061,7 @@
       </c>
       <c r="F41" s="1"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -6056,7 +6071,7 @@
       </c>
       <c r="F42" s="1"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -6066,7 +6081,7 @@
       </c>
       <c r="F43" s="1"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -6076,7 +6091,7 @@
       </c>
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -6086,7 +6101,7 @@
       </c>
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -6096,7 +6111,7 @@
       </c>
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -6106,7 +6121,7 @@
       </c>
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -6116,7 +6131,7 @@
       </c>
       <c r="F48" s="1"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -6126,7 +6141,7 @@
       </c>
       <c r="F49" s="1"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -6136,7 +6151,7 @@
       </c>
       <c r="F50" s="1"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -6154,9 +6169,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95515157-457C-45DA-8C75-1980CF080185}">
   <dimension ref="A1:J134"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>271</v>
       </c>
@@ -6186,7 +6201,7 @@
       </c>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2443</v>
       </c>
@@ -6216,7 +6231,7 @@
       </c>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -6236,7 +6251,7 @@
       </c>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -6256,7 +6271,7 @@
       </c>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -6276,7 +6291,7 @@
       </c>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -6296,7 +6311,7 @@
       </c>
       <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -6316,7 +6331,7 @@
       </c>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -6336,7 +6351,7 @@
       </c>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -6356,7 +6371,7 @@
       </c>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -6376,7 +6391,7 @@
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -6396,7 +6411,7 @@
       </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -6416,7 +6431,7 @@
       </c>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -6434,7 +6449,7 @@
       </c>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -6452,7 +6467,7 @@
       </c>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -6470,7 +6485,7 @@
       </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -6488,7 +6503,7 @@
       </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -6506,7 +6521,7 @@
       </c>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -6524,7 +6539,7 @@
       </c>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -6542,7 +6557,7 @@
       </c>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -6560,7 +6575,7 @@
       </c>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -6578,7 +6593,7 @@
       </c>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -6596,7 +6611,7 @@
       </c>
       <c r="J22" s="1"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -6614,7 +6629,7 @@
       </c>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -6632,7 +6647,7 @@
       </c>
       <c r="J24" s="1"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -6650,7 +6665,7 @@
       </c>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -6668,7 +6683,7 @@
       </c>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -6686,7 +6701,7 @@
       </c>
       <c r="J27" s="1"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -6704,7 +6719,7 @@
       </c>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -6722,7 +6737,7 @@
       </c>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -6740,7 +6755,7 @@
       </c>
       <c r="J30" s="1"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -6758,7 +6773,7 @@
       </c>
       <c r="J31" s="1"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -6776,7 +6791,7 @@
       </c>
       <c r="J32" s="1"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -6794,7 +6809,7 @@
       </c>
       <c r="J33" s="1"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -6812,7 +6827,7 @@
       </c>
       <c r="J34" s="1"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -6826,7 +6841,7 @@
       </c>
       <c r="J35" s="1"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -6840,7 +6855,7 @@
       </c>
       <c r="J36" s="1"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -6854,7 +6869,7 @@
       </c>
       <c r="J37" s="1"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -6868,7 +6883,7 @@
       </c>
       <c r="J38" s="1"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -6882,7 +6897,7 @@
       </c>
       <c r="J39" s="1"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -6896,7 +6911,7 @@
       </c>
       <c r="J40" s="1"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -6910,7 +6925,7 @@
       </c>
       <c r="J41" s="1"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -6924,7 +6939,7 @@
       </c>
       <c r="J42" s="1"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -6938,7 +6953,7 @@
       </c>
       <c r="J43" s="1"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -6952,7 +6967,7 @@
       </c>
       <c r="J44" s="1"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -6966,7 +6981,7 @@
       </c>
       <c r="J45" s="1"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -6980,7 +6995,7 @@
       </c>
       <c r="J46" s="1"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -6994,7 +7009,7 @@
       </c>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -7008,7 +7023,7 @@
       </c>
       <c r="J48" s="1"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -7022,7 +7037,7 @@
       </c>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -7036,7 +7051,7 @@
       </c>
       <c r="J50" s="1"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -7050,7 +7065,7 @@
       </c>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -7064,7 +7079,7 @@
       </c>
       <c r="J52" s="1"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -7078,7 +7093,7 @@
       </c>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -7092,7 +7107,7 @@
       </c>
       <c r="J54" s="1"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -7106,7 +7121,7 @@
       </c>
       <c r="J55" s="1"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -7120,7 +7135,7 @@
       </c>
       <c r="J56" s="1"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -7134,7 +7149,7 @@
       </c>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -7148,7 +7163,7 @@
       </c>
       <c r="J58" s="1"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -7162,7 +7177,7 @@
       </c>
       <c r="J59" s="1"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -7176,7 +7191,7 @@
       </c>
       <c r="J60" s="1"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -7190,7 +7205,7 @@
       </c>
       <c r="J61" s="1"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -7204,7 +7219,7 @@
       </c>
       <c r="J62" s="1"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -7218,7 +7233,7 @@
       </c>
       <c r="J63" s="1"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -7232,7 +7247,7 @@
       </c>
       <c r="J64" s="1"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -7246,7 +7261,7 @@
       </c>
       <c r="J65" s="1"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -7260,7 +7275,7 @@
       </c>
       <c r="J66" s="1"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -7274,7 +7289,7 @@
       </c>
       <c r="J67" s="1"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -7288,7 +7303,7 @@
       </c>
       <c r="J68" s="1"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -7302,7 +7317,7 @@
       </c>
       <c r="J69" s="1"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -7316,7 +7331,7 @@
       </c>
       <c r="J70" s="1"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -7330,7 +7345,7 @@
       </c>
       <c r="J71" s="1"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -7344,7 +7359,7 @@
       </c>
       <c r="J72" s="1"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -7358,7 +7373,7 @@
       </c>
       <c r="J73" s="1"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -7372,7 +7387,7 @@
       </c>
       <c r="J74" s="1"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -7386,7 +7401,7 @@
       </c>
       <c r="J75" s="1"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -7400,7 +7415,7 @@
       </c>
       <c r="J76" s="1"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -7414,7 +7429,7 @@
       </c>
       <c r="J77" s="1"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -7428,7 +7443,7 @@
       </c>
       <c r="J78" s="1"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -7442,7 +7457,7 @@
       </c>
       <c r="J79" s="1"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -7456,7 +7471,7 @@
       </c>
       <c r="J80" s="1"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -7470,7 +7485,7 @@
       </c>
       <c r="J81" s="1"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -7484,7 +7499,7 @@
       </c>
       <c r="J82" s="1"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -7498,7 +7513,7 @@
       </c>
       <c r="J83" s="1"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -7512,7 +7527,7 @@
       </c>
       <c r="J84" s="1"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -7526,7 +7541,7 @@
       </c>
       <c r="J85" s="1"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -7540,7 +7555,7 @@
       </c>
       <c r="J86" s="1"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -7554,7 +7569,7 @@
       </c>
       <c r="J87" s="1"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -7568,7 +7583,7 @@
       </c>
       <c r="J88" s="1"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -7582,7 +7597,7 @@
       </c>
       <c r="J89" s="1"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -7596,7 +7611,7 @@
       </c>
       <c r="J90" s="1"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -7610,7 +7625,7 @@
       </c>
       <c r="J91" s="1"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -7624,7 +7639,7 @@
       </c>
       <c r="J92" s="1"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -7638,7 +7653,7 @@
       </c>
       <c r="J93" s="1"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -7652,7 +7667,7 @@
       </c>
       <c r="J94" s="1"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -7666,7 +7681,7 @@
       </c>
       <c r="J95" s="1"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -7680,7 +7695,7 @@
       </c>
       <c r="J96" s="1"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -7694,7 +7709,7 @@
       </c>
       <c r="J97" s="1"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -7708,7 +7723,7 @@
       </c>
       <c r="J98" s="1"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -7722,7 +7737,7 @@
       </c>
       <c r="J99" s="1"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -7736,7 +7751,7 @@
       </c>
       <c r="J100" s="1"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -7750,7 +7765,7 @@
       </c>
       <c r="J101" s="1"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -7764,7 +7779,7 @@
       </c>
       <c r="J102" s="1"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -7778,7 +7793,7 @@
       </c>
       <c r="J103" s="1"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -7792,7 +7807,7 @@
       </c>
       <c r="J104" s="1"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -7806,7 +7821,7 @@
       </c>
       <c r="J105" s="1"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -7820,7 +7835,7 @@
       </c>
       <c r="J106" s="1"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -7834,7 +7849,7 @@
       </c>
       <c r="J107" s="1"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -7848,7 +7863,7 @@
       </c>
       <c r="J108" s="1"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -7862,7 +7877,7 @@
       </c>
       <c r="J109" s="1"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -7876,7 +7891,7 @@
       </c>
       <c r="J110" s="1"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -7890,7 +7905,7 @@
       </c>
       <c r="J111" s="1"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -7904,7 +7919,7 @@
       </c>
       <c r="J112" s="1"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -7918,7 +7933,7 @@
       </c>
       <c r="J113" s="1"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -7932,7 +7947,7 @@
       </c>
       <c r="J114" s="1"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -7946,7 +7961,7 @@
       </c>
       <c r="J115" s="1"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -7960,7 +7975,7 @@
       </c>
       <c r="J116" s="1"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -7974,7 +7989,7 @@
       </c>
       <c r="J117" s="1"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -7988,7 +8003,7 @@
       </c>
       <c r="J118" s="1"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -8002,7 +8017,7 @@
       </c>
       <c r="J119" s="1"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -8016,7 +8031,7 @@
       </c>
       <c r="J120" s="1"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -8030,7 +8045,7 @@
       </c>
       <c r="J121" s="1"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -8044,7 +8059,7 @@
       </c>
       <c r="J122" s="1"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -8058,7 +8073,7 @@
       </c>
       <c r="J123" s="1"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -8072,7 +8087,7 @@
       </c>
       <c r="J124" s="1"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -8086,7 +8101,7 @@
       </c>
       <c r="J125" s="1"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -8100,7 +8115,7 @@
       </c>
       <c r="J126" s="1"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -8114,7 +8129,7 @@
       </c>
       <c r="J127" s="1"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -8128,7 +8143,7 @@
       </c>
       <c r="J128" s="1"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -8142,7 +8157,7 @@
       </c>
       <c r="J129" s="1"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -8156,7 +8171,7 @@
       </c>
       <c r="J130" s="1"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -8170,7 +8185,7 @@
       </c>
       <c r="J131" s="1"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -8184,7 +8199,7 @@
       </c>
       <c r="J132" s="1"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -8198,7 +8213,7 @@
       </c>
       <c r="J133" s="1"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
